--- a/orders.xlsx
+++ b/orders.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
           <t>total</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>promo_code</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,6 +513,62 @@
       </c>
       <c r="F2" t="n">
         <v>36</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:42:12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kljjh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>mnmm</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Urban Bites Kitchen - Smoky House Burger x1 [Bun: 1, Beef Patty: 1, Cheddar: 1, Onions: 2, Sauce: 1] ($14.00) | Urban Bites Kitchen - Smoky House Burger x1 [Bun: 0, Beef Patty: 1, Cheddar: 1, Onions: 2, Sauce: 1] ($13.25)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Urban Bites Kitchen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
